--- a/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-LST-02_ertelenen_bakim_gorevleri_takip_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/01_MAI1 - Bakım Planı ve Gerçekleşme/EKG-BAK-LST-02_ertelenen_bakim_gorevleri_takip_listesi.xlsx
@@ -860,7 +860,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-LST-02&amp;C&amp;"Arial,Regular"&amp;11Ertelenen Bakım Görevleri Takip Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 24.09.2026
+Revizyon nedeni: Erteleme listesi risk değerlendirmesi, geçici kontrol, yetkili onay ve kapanış kanıtı üzerinden düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
